--- a/olah/Raw_Data_Dump_2022-2024 No Outlier.xlsx
+++ b/olah/Raw_Data_Dump_2022-2024 No Outlier.xlsx
@@ -1,24 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Malik\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calcifer/Documents/MDMA/olah/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D67CADE5-6866-47A5-822D-E2E4B4654C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4229F8A0-2C21-604E-BDDA-B96F484DEB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AN$640</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AN$641</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1352,6 +1365,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1696,15 +1710,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN640"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AN642"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="15" max="15" width="32.85546875" customWidth="1"/>
-    <col min="16" max="16" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.83203125" customWidth="1"/>
+    <col min="16" max="16" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1826,7 +1843,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -1948,7 +1965,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -2070,7 +2087,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -2192,7 +2209,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>184</v>
       </c>
@@ -2314,7 +2331,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>379</v>
       </c>
@@ -2436,7 +2453,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>380</v>
       </c>
@@ -2558,7 +2575,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>337</v>
       </c>
@@ -2680,7 +2697,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>185</v>
       </c>
@@ -2802,7 +2819,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>381</v>
       </c>
@@ -2924,7 +2941,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>183</v>
       </c>
@@ -3046,7 +3063,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>186</v>
       </c>
@@ -3168,7 +3185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>189</v>
       </c>
@@ -3290,7 +3307,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -3412,7 +3429,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -3534,7 +3551,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>382</v>
       </c>
@@ -3656,7 +3673,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -3778,7 +3795,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>190</v>
       </c>
@@ -3900,7 +3917,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>339</v>
       </c>
@@ -4022,7 +4039,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -4144,7 +4161,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>192</v>
       </c>
@@ -4266,7 +4283,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>383</v>
       </c>
@@ -4388,7 +4405,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>340</v>
       </c>
@@ -4510,7 +4527,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>193</v>
       </c>
@@ -4632,7 +4649,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -4754,7 +4771,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>194</v>
       </c>
@@ -4876,7 +4893,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -4998,7 +5015,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>195</v>
       </c>
@@ -5120,7 +5137,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -5242,7 +5259,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -5364,7 +5381,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>198</v>
       </c>
@@ -5486,7 +5503,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>199</v>
       </c>
@@ -5608,7 +5625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -5730,7 +5747,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>191</v>
       </c>
@@ -5852,7 +5869,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -5974,7 +5991,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>197</v>
       </c>
@@ -6096,7 +6113,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>59</v>
       </c>
@@ -6218,7 +6235,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -6340,7 +6357,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>63</v>
       </c>
@@ -6462,7 +6479,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>205</v>
       </c>
@@ -6584,7 +6601,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>196</v>
       </c>
@@ -6706,7 +6723,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>58</v>
       </c>
@@ -6828,7 +6845,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>210</v>
       </c>
@@ -6950,7 +6967,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>208</v>
       </c>
@@ -7072,7 +7089,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>65</v>
       </c>
@@ -7194,7 +7211,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>204</v>
       </c>
@@ -7316,7 +7333,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>203</v>
       </c>
@@ -7438,7 +7455,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -7560,7 +7577,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>384</v>
       </c>
@@ -7682,7 +7699,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>343</v>
       </c>
@@ -7804,7 +7821,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>70</v>
       </c>
@@ -7926,7 +7943,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>346</v>
       </c>
@@ -8048,7 +8065,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>219</v>
       </c>
@@ -8170,7 +8187,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>385</v>
       </c>
@@ -8292,7 +8309,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -8414,7 +8431,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>214</v>
       </c>
@@ -8536,7 +8553,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>209</v>
       </c>
@@ -8658,7 +8675,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>217</v>
       </c>
@@ -8780,7 +8797,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>213</v>
       </c>
@@ -8902,7 +8919,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>386</v>
       </c>
@@ -9024,7 +9041,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>215</v>
       </c>
@@ -9146,7 +9163,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -9268,7 +9285,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -9390,7 +9407,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>220</v>
       </c>
@@ -9512,7 +9529,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>345</v>
       </c>
@@ -9634,7 +9651,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>72</v>
       </c>
@@ -9756,7 +9773,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>218</v>
       </c>
@@ -9878,7 +9895,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -10000,7 +10017,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>222</v>
       </c>
@@ -10122,7 +10139,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -10244,7 +10261,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>224</v>
       </c>
@@ -10366,7 +10383,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -10488,7 +10505,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>223</v>
       </c>
@@ -10610,7 +10627,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="74" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>348</v>
       </c>
@@ -10732,7 +10749,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>66</v>
       </c>
@@ -10854,7 +10871,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>387</v>
       </c>
@@ -10976,7 +10993,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="77" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>82</v>
       </c>
@@ -11098,7 +11115,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="78" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -11220,7 +11237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -11342,7 +11359,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>107</v>
       </c>
@@ -11464,7 +11481,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>225</v>
       </c>
@@ -11586,7 +11603,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>230</v>
       </c>
@@ -11708,7 +11725,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>351</v>
       </c>
@@ -11830,7 +11847,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -11952,7 +11969,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="85" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -12074,7 +12091,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -12196,7 +12213,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -12318,7 +12335,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -12440,7 +12457,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>388</v>
       </c>
@@ -12562,7 +12579,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>90</v>
       </c>
@@ -12684,7 +12701,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="91" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -12806,7 +12823,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -12928,7 +12945,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="93" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>226</v>
       </c>
@@ -13050,7 +13067,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="94" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>352</v>
       </c>
@@ -13172,7 +13189,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -13294,7 +13311,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="96" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>235</v>
       </c>
@@ -13416,7 +13433,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>236</v>
       </c>
@@ -13538,7 +13555,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>233</v>
       </c>
@@ -13660,7 +13677,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>389</v>
       </c>
@@ -13782,7 +13799,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="100" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>243</v>
       </c>
@@ -13904,7 +13921,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>238</v>
       </c>
@@ -14026,7 +14043,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>239</v>
       </c>
@@ -14148,7 +14165,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="103" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>390</v>
       </c>
@@ -14270,7 +14287,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>94</v>
       </c>
@@ -14392,7 +14409,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="105" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>97</v>
       </c>
@@ -14514,7 +14531,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>98</v>
       </c>
@@ -14636,7 +14653,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="107" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>247</v>
       </c>
@@ -14758,7 +14775,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="108" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>77</v>
       </c>
@@ -14880,7 +14897,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="109" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>227</v>
       </c>
@@ -15002,7 +15019,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="110" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>96</v>
       </c>
@@ -15124,7 +15141,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="111" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>99</v>
       </c>
@@ -15246,7 +15263,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>101</v>
       </c>
@@ -15368,7 +15385,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>240</v>
       </c>
@@ -15490,7 +15507,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="114" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>245</v>
       </c>
@@ -15612,7 +15629,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>248</v>
       </c>
@@ -15734,7 +15751,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>391</v>
       </c>
@@ -15856,7 +15873,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="117" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>249</v>
       </c>
@@ -15978,7 +15995,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="118" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>355</v>
       </c>
@@ -16100,7 +16117,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="119" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>103</v>
       </c>
@@ -16222,7 +16239,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="120" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>251</v>
       </c>
@@ -16344,7 +16361,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="121" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>105</v>
       </c>
@@ -16466,7 +16483,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="122" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>257</v>
       </c>
@@ -16588,7 +16605,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="123" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>106</v>
       </c>
@@ -16710,7 +16727,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="124" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>357</v>
       </c>
@@ -16832,7 +16849,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="125" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>250</v>
       </c>
@@ -16954,7 +16971,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="126" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>110</v>
       </c>
@@ -17076,7 +17093,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>112</v>
       </c>
@@ -17198,7 +17215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="128" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>109</v>
       </c>
@@ -17320,7 +17337,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="129" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>254</v>
       </c>
@@ -17442,7 +17459,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>114</v>
       </c>
@@ -17564,7 +17581,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="131" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>361</v>
       </c>
@@ -17686,7 +17703,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="132" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>116</v>
       </c>
@@ -17808,7 +17825,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="133" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>258</v>
       </c>
@@ -17930,7 +17947,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>115</v>
       </c>
@@ -18052,7 +18069,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="135" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>111</v>
       </c>
@@ -18174,7 +18191,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="136" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>393</v>
       </c>
@@ -18296,7 +18313,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="137" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>394</v>
       </c>
@@ -18418,7 +18435,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="138" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>395</v>
       </c>
@@ -18540,7 +18557,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="139" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>117</v>
       </c>
@@ -18662,7 +18679,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="140" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>120</v>
       </c>
@@ -18784,7 +18801,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="141" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>397</v>
       </c>
@@ -18906,7 +18923,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="142" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>121</v>
       </c>
@@ -19028,7 +19045,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="143" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>398</v>
       </c>
@@ -19150,7 +19167,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>122</v>
       </c>
@@ -19272,7 +19289,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>123</v>
       </c>
@@ -19394,7 +19411,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="146" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>124</v>
       </c>
@@ -19516,7 +19533,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="147" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>128</v>
       </c>
@@ -19638,7 +19655,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>127</v>
       </c>
@@ -19760,7 +19777,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="149" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>263</v>
       </c>
@@ -19882,7 +19899,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="150" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>399</v>
       </c>
@@ -20004,7 +20021,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>262</v>
       </c>
@@ -20126,7 +20143,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="152" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>130</v>
       </c>
@@ -20248,7 +20265,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>260</v>
       </c>
@@ -20370,7 +20387,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="154" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>275</v>
       </c>
@@ -20492,7 +20509,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="155" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>264</v>
       </c>
@@ -20614,7 +20631,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="156" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>363</v>
       </c>
@@ -20736,7 +20753,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>261</v>
       </c>
@@ -20858,7 +20875,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="158" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>125</v>
       </c>
@@ -20980,7 +20997,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="159" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>401</v>
       </c>
@@ -21102,7 +21119,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="160" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>268</v>
       </c>
@@ -21224,7 +21241,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>266</v>
       </c>
@@ -21346,7 +21363,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="162" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>131</v>
       </c>
@@ -21468,7 +21485,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="163" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>134</v>
       </c>
@@ -21590,7 +21607,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="164" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>269</v>
       </c>
@@ -21712,7 +21729,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="165" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>402</v>
       </c>
@@ -21834,7 +21851,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="166" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>133</v>
       </c>
@@ -21956,7 +21973,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="167" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>267</v>
       </c>
@@ -22078,7 +22095,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="168" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>404</v>
       </c>
@@ -22200,7 +22217,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="169" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>364</v>
       </c>
@@ -22322,7 +22339,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="170" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>273</v>
       </c>
@@ -22444,7 +22461,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="171" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>369</v>
       </c>
@@ -22566,7 +22583,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>270</v>
       </c>
@@ -22688,7 +22705,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="173" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>276</v>
       </c>
@@ -22810,7 +22827,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="174" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>132</v>
       </c>
@@ -22932,7 +22949,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="175" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>278</v>
       </c>
@@ -23054,7 +23071,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>135</v>
       </c>
@@ -23176,7 +23193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="177" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>137</v>
       </c>
@@ -23298,7 +23315,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>136</v>
       </c>
@@ -23420,7 +23437,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="179" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>405</v>
       </c>
@@ -23542,7 +23559,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>277</v>
       </c>
@@ -23664,7 +23681,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>139</v>
       </c>
@@ -23786,7 +23803,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="182" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>142</v>
       </c>
@@ -23908,7 +23925,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="183" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>368</v>
       </c>
@@ -24030,7 +24047,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>143</v>
       </c>
@@ -24152,7 +24169,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="185" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>281</v>
       </c>
@@ -24274,7 +24291,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="186" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>144</v>
       </c>
@@ -24396,7 +24413,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="187" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>141</v>
       </c>
@@ -24518,7 +24535,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>140</v>
       </c>
@@ -24640,7 +24657,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="189" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>280</v>
       </c>
@@ -24762,7 +24779,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="190" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>145</v>
       </c>
@@ -24884,7 +24901,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="191" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>283</v>
       </c>
@@ -25006,7 +25023,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="192" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>406</v>
       </c>
@@ -25128,7 +25145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>293</v>
       </c>
@@ -25250,7 +25267,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>285</v>
       </c>
@@ -25372,7 +25389,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="195" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>282</v>
       </c>
@@ -25494,7 +25511,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="196" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>286</v>
       </c>
@@ -25616,7 +25633,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="197" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>148</v>
       </c>
@@ -25738,7 +25755,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>372</v>
       </c>
@@ -25860,7 +25877,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>138</v>
       </c>
@@ -25982,7 +25999,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="200" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>294</v>
       </c>
@@ -26104,7 +26121,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="201" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>146</v>
       </c>
@@ -26226,7 +26243,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="202" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>407</v>
       </c>
@@ -26348,7 +26365,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="203" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>408</v>
       </c>
@@ -26470,7 +26487,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>409</v>
       </c>
@@ -26592,7 +26609,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="205" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>290</v>
       </c>
@@ -26714,7 +26731,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="206" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>147</v>
       </c>
@@ -26836,7 +26853,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="207" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>410</v>
       </c>
@@ -26958,7 +26975,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="208" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>292</v>
       </c>
@@ -27080,7 +27097,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="209" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>287</v>
       </c>
@@ -27202,7 +27219,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="210" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>303</v>
       </c>
@@ -27324,7 +27341,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="211" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>291</v>
       </c>
@@ -27446,7 +27463,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>288</v>
       </c>
@@ -27568,7 +27585,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="213" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>150</v>
       </c>
@@ -27690,7 +27707,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="214" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>153</v>
       </c>
@@ -27812,7 +27829,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="215" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>301</v>
       </c>
@@ -27934,7 +27951,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>298</v>
       </c>
@@ -28056,7 +28073,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="217" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>296</v>
       </c>
@@ -28178,7 +28195,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="218" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>306</v>
       </c>
@@ -28300,7 +28317,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="219" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>151</v>
       </c>
@@ -28422,7 +28439,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>308</v>
       </c>
@@ -28544,7 +28561,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="221" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>156</v>
       </c>
@@ -28666,7 +28683,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="222" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>299</v>
       </c>
@@ -28788,7 +28805,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="223" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>411</v>
       </c>
@@ -28910,7 +28927,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="224" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>304</v>
       </c>
@@ -29032,7 +29049,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="225" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>374</v>
       </c>
@@ -29154,7 +29171,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="226" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>310</v>
       </c>
@@ -29276,7 +29293,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>158</v>
       </c>
@@ -29398,7 +29415,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="228" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>159</v>
       </c>
@@ -29520,7 +29537,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="229" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>155</v>
       </c>
@@ -29642,7 +29659,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>302</v>
       </c>
@@ -29764,7 +29781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>160</v>
       </c>
@@ -29886,7 +29903,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="232" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>305</v>
       </c>
@@ -30008,7 +30025,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="233" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>300</v>
       </c>
@@ -30130,7 +30147,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="234" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>318</v>
       </c>
@@ -30252,7 +30269,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="235" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>412</v>
       </c>
@@ -30374,7 +30391,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="236" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>312</v>
       </c>
@@ -30496,7 +30513,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="237" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>157</v>
       </c>
@@ -30618,7 +30635,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="238" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>316</v>
       </c>
@@ -30740,7 +30757,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="239" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>329</v>
       </c>
@@ -30862,7 +30879,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="240" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>161</v>
       </c>
@@ -30984,7 +31001,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="241" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>315</v>
       </c>
@@ -31106,7 +31123,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="242" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>166</v>
       </c>
@@ -31228,7 +31245,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="243" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>163</v>
       </c>
@@ -31350,7 +31367,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="244" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>313</v>
       </c>
@@ -31472,7 +31489,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="245" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>164</v>
       </c>
@@ -31594,7 +31611,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="246" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>317</v>
       </c>
@@ -31716,7 +31733,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="247" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>167</v>
       </c>
@@ -31838,7 +31855,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="248" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>168</v>
       </c>
@@ -31960,7 +31977,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>314</v>
       </c>
@@ -32082,7 +32099,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>321</v>
       </c>
@@ -32204,7 +32221,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="251" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>319</v>
       </c>
@@ -32326,7 +32343,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="252" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>172</v>
       </c>
@@ -32448,7 +32465,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="253" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>162</v>
       </c>
@@ -32570,7 +32587,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="254" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>173</v>
       </c>
@@ -32692,7 +32709,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="255" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>169</v>
       </c>
@@ -32814,7 +32831,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="256" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>320</v>
       </c>
@@ -32936,7 +32953,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="257" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>174</v>
       </c>
@@ -33058,7 +33075,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>377</v>
       </c>
@@ -33180,7 +33197,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="259" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>170</v>
       </c>
@@ -33302,7 +33319,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="260" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>165</v>
       </c>
@@ -33424,7 +33441,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="261" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>325</v>
       </c>
@@ -33546,7 +33563,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="262" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>176</v>
       </c>
@@ -33668,7 +33685,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="263" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>171</v>
       </c>
@@ -33790,7 +33807,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="264" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>178</v>
       </c>
@@ -33912,7 +33929,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>413</v>
       </c>
@@ -34034,7 +34051,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="266" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>177</v>
       </c>
@@ -34156,7 +34173,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="267" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>175</v>
       </c>
@@ -34278,7 +34295,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="268" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>324</v>
       </c>
@@ -34400,7 +34417,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="269" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>334</v>
       </c>
@@ -34522,7 +34539,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="270" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>322</v>
       </c>
@@ -34644,7 +34661,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="271" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>327</v>
       </c>
@@ -34766,7 +34783,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="272" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>181</v>
       </c>
@@ -34888,7 +34905,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="273" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>335</v>
       </c>
@@ -35010,7 +35027,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="274" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>336</v>
       </c>
@@ -35132,7 +35149,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="275" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>415</v>
       </c>
@@ -35254,7 +35271,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="276" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>333</v>
       </c>
@@ -35376,7 +35393,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="277" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>331</v>
       </c>
@@ -35498,7 +35515,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="278" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>180</v>
       </c>
@@ -35620,7 +35637,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="279" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>332</v>
       </c>
@@ -35742,7 +35759,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="280" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>378</v>
       </c>
@@ -35864,7 +35881,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>41</v>
       </c>
@@ -35986,7 +36003,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="282" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>416</v>
       </c>
@@ -36108,7 +36125,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="283" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>46</v>
       </c>
@@ -36230,7 +36247,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="284" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>380</v>
       </c>
@@ -36352,7 +36369,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="285" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>45</v>
       </c>
@@ -36474,7 +36491,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="286" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>379</v>
       </c>
@@ -36596,7 +36613,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="287" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>183</v>
       </c>
@@ -36718,7 +36735,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="288" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>44</v>
       </c>
@@ -36840,7 +36857,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="289" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>417</v>
       </c>
@@ -36962,7 +36979,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="290" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>182</v>
       </c>
@@ -37084,7 +37101,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="291" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>186</v>
       </c>
@@ -37206,7 +37223,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="292" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>339</v>
       </c>
@@ -37328,7 +37345,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="293" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>185</v>
       </c>
@@ -37450,7 +37467,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="294" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>189</v>
       </c>
@@ -37572,7 +37589,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="295" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>190</v>
       </c>
@@ -37694,7 +37711,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="296" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>51</v>
       </c>
@@ -37816,7 +37833,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="297" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>187</v>
       </c>
@@ -37938,7 +37955,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="298" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>381</v>
       </c>
@@ -38060,7 +38077,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="299" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>49</v>
       </c>
@@ -38182,7 +38199,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="300" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>52</v>
       </c>
@@ -38304,7 +38321,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="301" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>418</v>
       </c>
@@ -38426,7 +38443,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="302" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>42</v>
       </c>
@@ -38548,7 +38565,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="303" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>188</v>
       </c>
@@ -38670,7 +38687,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="304" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>192</v>
       </c>
@@ -38792,7 +38809,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="305" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>340</v>
       </c>
@@ -38914,7 +38931,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="306" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>419</v>
       </c>
@@ -39036,7 +39053,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="307" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>420</v>
       </c>
@@ -39158,7 +39175,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="308" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>191</v>
       </c>
@@ -39280,7 +39297,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="309" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>382</v>
       </c>
@@ -39402,7 +39419,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="310" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>193</v>
       </c>
@@ -39524,7 +39541,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="311" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>50</v>
       </c>
@@ -39646,7 +39663,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="312" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>54</v>
       </c>
@@ -39768,7 +39785,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="313" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>57</v>
       </c>
@@ -39890,7 +39907,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="314" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>56</v>
       </c>
@@ -40012,7 +40029,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="315" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>341</v>
       </c>
@@ -40134,7 +40151,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="316" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>198</v>
       </c>
@@ -40256,7 +40273,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="317" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>53</v>
       </c>
@@ -40378,7 +40395,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="318" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>197</v>
       </c>
@@ -40500,7 +40517,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="319" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>207</v>
       </c>
@@ -40622,7 +40639,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="320" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>199</v>
       </c>
@@ -40744,7 +40761,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="321" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>58</v>
       </c>
@@ -40866,7 +40883,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="322" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>194</v>
       </c>
@@ -40988,7 +41005,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="323" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>196</v>
       </c>
@@ -41110,7 +41127,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="324" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>59</v>
       </c>
@@ -41232,7 +41249,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="325" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>60</v>
       </c>
@@ -41354,7 +41371,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="326" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>55</v>
       </c>
@@ -41476,7 +41493,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="327" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>384</v>
       </c>
@@ -41598,7 +41615,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="328" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>421</v>
       </c>
@@ -41720,7 +41737,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="329" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>200</v>
       </c>
@@ -41842,7 +41859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="330" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>203</v>
       </c>
@@ -41964,7 +41981,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="331" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>208</v>
       </c>
@@ -42086,7 +42103,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="332" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>205</v>
       </c>
@@ -42208,7 +42225,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="333" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>66</v>
       </c>
@@ -42330,7 +42347,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="334" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>206</v>
       </c>
@@ -42452,7 +42469,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="335" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>201</v>
       </c>
@@ -42574,7 +42591,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="336" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>63</v>
       </c>
@@ -42696,7 +42713,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="337" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>422</v>
       </c>
@@ -42818,7 +42835,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="338" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>204</v>
       </c>
@@ -42940,7 +42957,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="339" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>62</v>
       </c>
@@ -43062,7 +43079,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="340" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>210</v>
       </c>
@@ -43184,7 +43201,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="341" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>61</v>
       </c>
@@ -43306,7 +43323,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="342" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>217</v>
       </c>
@@ -43428,7 +43445,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="343" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>202</v>
       </c>
@@ -43550,7 +43567,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="344" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>212</v>
       </c>
@@ -43672,7 +43689,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="345" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>69</v>
       </c>
@@ -43794,7 +43811,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="346" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>385</v>
       </c>
@@ -43916,7 +43933,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="347" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>67</v>
       </c>
@@ -44038,7 +44055,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="348" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>346</v>
       </c>
@@ -44160,7 +44177,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="349" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>342</v>
       </c>
@@ -44282,7 +44299,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="350" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>211</v>
       </c>
@@ -44404,7 +44421,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="351" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>214</v>
       </c>
@@ -44526,7 +44543,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="352" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>209</v>
       </c>
@@ -44648,7 +44665,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="353" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>215</v>
       </c>
@@ -44770,7 +44787,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="354" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>64</v>
       </c>
@@ -44892,7 +44909,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="355" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>65</v>
       </c>
@@ -45014,7 +45031,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="356" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>344</v>
       </c>
@@ -45136,7 +45153,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="357" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>216</v>
       </c>
@@ -45258,7 +45275,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="358" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>70</v>
       </c>
@@ -45380,7 +45397,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="359" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>343</v>
       </c>
@@ -45502,7 +45519,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="360" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>386</v>
       </c>
@@ -45624,7 +45641,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="361" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>75</v>
       </c>
@@ -45746,7 +45763,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="362" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>68</v>
       </c>
@@ -45868,7 +45885,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="363" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>213</v>
       </c>
@@ -45990,7 +46007,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="364" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>423</v>
       </c>
@@ -46112,7 +46129,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="365" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>424</v>
       </c>
@@ -46234,7 +46251,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="366" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>219</v>
       </c>
@@ -46356,7 +46373,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="367" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>425</v>
       </c>
@@ -46478,7 +46495,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="368" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>345</v>
       </c>
@@ -46600,7 +46617,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="369" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>72</v>
       </c>
@@ -46722,7 +46739,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="370" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>347</v>
       </c>
@@ -46844,7 +46861,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="371" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>220</v>
       </c>
@@ -46966,7 +46983,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="372" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>221</v>
       </c>
@@ -47088,7 +47105,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="373" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>74</v>
       </c>
@@ -47210,7 +47227,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="374" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>78</v>
       </c>
@@ -47332,7 +47349,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="375" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>77</v>
       </c>
@@ -47454,7 +47471,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="376" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>76</v>
       </c>
@@ -47576,7 +47593,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="377" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>224</v>
       </c>
@@ -47698,7 +47715,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="378" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>387</v>
       </c>
@@ -47820,7 +47837,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="379" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>225</v>
       </c>
@@ -47942,7 +47959,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="380" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>223</v>
       </c>
@@ -48064,7 +48081,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="381" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>81</v>
       </c>
@@ -48186,7 +48203,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="382" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>222</v>
       </c>
@@ -48308,7 +48325,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="383" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>348</v>
       </c>
@@ -48430,7 +48447,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="384" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>226</v>
       </c>
@@ -48552,7 +48569,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="385" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>228</v>
       </c>
@@ -48674,7 +48691,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="386" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>349</v>
       </c>
@@ -48796,7 +48813,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="387" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>227</v>
       </c>
@@ -48918,7 +48935,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="388" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>350</v>
       </c>
@@ -49040,7 +49057,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="389" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>82</v>
       </c>
@@ -49162,7 +49179,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="390" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>79</v>
       </c>
@@ -49284,7 +49301,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="391" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>85</v>
       </c>
@@ -49406,7 +49423,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="392" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>83</v>
       </c>
@@ -49528,7 +49545,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="393" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>230</v>
       </c>
@@ -49650,7 +49667,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="394" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>84</v>
       </c>
@@ -49772,7 +49789,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="395" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>86</v>
       </c>
@@ -49894,7 +49911,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="396" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>351</v>
       </c>
@@ -50016,7 +50033,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="397" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>71</v>
       </c>
@@ -50138,7 +50155,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="398" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>80</v>
       </c>
@@ -50260,7 +50277,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="399" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>87</v>
       </c>
@@ -50382,7 +50399,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="400" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>89</v>
       </c>
@@ -50504,7 +50521,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="401" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>426</v>
       </c>
@@ -50626,7 +50643,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="402" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>88</v>
       </c>
@@ -50748,7 +50765,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="403" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>229</v>
       </c>
@@ -50870,7 +50887,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="404" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>91</v>
       </c>
@@ -50992,7 +51009,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="405" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>90</v>
       </c>
@@ -51114,7 +51131,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="406" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>388</v>
       </c>
@@ -51236,7 +51253,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="407" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>353</v>
       </c>
@@ -51358,7 +51375,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="408" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>92</v>
       </c>
@@ -51480,7 +51497,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="409" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>232</v>
       </c>
@@ -51602,7 +51619,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="410" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>231</v>
       </c>
@@ -51724,7 +51741,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="411" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>235</v>
       </c>
@@ -51846,7 +51863,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="412" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>236</v>
       </c>
@@ -51968,7 +51985,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="413" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>237</v>
       </c>
@@ -52090,7 +52107,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="414" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>243</v>
       </c>
@@ -52212,7 +52229,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="415" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>354</v>
       </c>
@@ -52334,7 +52351,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="416" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>352</v>
       </c>
@@ -52456,7 +52473,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="417" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>389</v>
       </c>
@@ -52578,7 +52595,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="418" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>233</v>
       </c>
@@ -52700,7 +52717,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="419" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>238</v>
       </c>
@@ -52822,7 +52839,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="420" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>234</v>
       </c>
@@ -52944,7 +52961,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="421" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>95</v>
       </c>
@@ -53066,7 +53083,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="422" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>93</v>
       </c>
@@ -53188,7 +53205,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="423" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>96</v>
       </c>
@@ -53310,7 +53327,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="424" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>390</v>
       </c>
@@ -53432,7 +53449,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="425" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>94</v>
       </c>
@@ -53554,7 +53571,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="426" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>240</v>
       </c>
@@ -53676,7 +53693,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="427" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>97</v>
       </c>
@@ -53798,7 +53815,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="428" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>99</v>
       </c>
@@ -53920,7 +53937,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="429" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>244</v>
       </c>
@@ -54042,7 +54059,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="430" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>241</v>
       </c>
@@ -54164,7 +54181,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="431" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>391</v>
       </c>
@@ -54286,7 +54303,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="432" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>101</v>
       </c>
@@ -54408,7 +54425,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="433" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>245</v>
       </c>
@@ -54530,7 +54547,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="434" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>100</v>
       </c>
@@ -54652,7 +54669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="435" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>427</v>
       </c>
@@ -54774,7 +54791,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="436" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>248</v>
       </c>
@@ -54896,7 +54913,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="437" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>239</v>
       </c>
@@ -55018,7 +55035,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="438" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>102</v>
       </c>
@@ -55140,7 +55157,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="439" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>246</v>
       </c>
@@ -55262,7 +55279,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="440" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>104</v>
       </c>
@@ -55384,7 +55401,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="441" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>249</v>
       </c>
@@ -55506,7 +55523,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="442" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>355</v>
       </c>
@@ -55628,7 +55645,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="443" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>98</v>
       </c>
@@ -55750,7 +55767,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="444" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>252</v>
       </c>
@@ -55872,7 +55889,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="445" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>254</v>
       </c>
@@ -55994,7 +56011,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="446" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>105</v>
       </c>
@@ -56116,7 +56133,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="447" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>242</v>
       </c>
@@ -56238,7 +56255,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="448" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>255</v>
       </c>
@@ -56360,7 +56377,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="449" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>103</v>
       </c>
@@ -56482,7 +56499,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="450" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>253</v>
       </c>
@@ -56604,7 +56621,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="451" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>360</v>
       </c>
@@ -56726,7 +56743,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="452" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>356</v>
       </c>
@@ -56848,7 +56865,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="453" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>109</v>
       </c>
@@ -56970,7 +56987,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="454" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>392</v>
       </c>
@@ -57092,7 +57109,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="455" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>357</v>
       </c>
@@ -57214,7 +57231,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="456" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>110</v>
       </c>
@@ -57336,7 +57353,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="457" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>112</v>
       </c>
@@ -57458,7 +57475,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="458" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>256</v>
       </c>
@@ -57580,7 +57597,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="459" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>111</v>
       </c>
@@ -57702,7 +57719,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="460" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>113</v>
       </c>
@@ -57824,7 +57841,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="461" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>108</v>
       </c>
@@ -57946,7 +57963,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="462" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>358</v>
       </c>
@@ -58068,7 +58085,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="463" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>251</v>
       </c>
@@ -58190,7 +58207,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="464" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>114</v>
       </c>
@@ -58312,7 +58329,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="465" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>258</v>
       </c>
@@ -58434,7 +58451,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="466" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>257</v>
       </c>
@@ -58556,7 +58573,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="467" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>116</v>
       </c>
@@ -58678,7 +58695,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="468" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>115</v>
       </c>
@@ -58800,7 +58817,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="469" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>359</v>
       </c>
@@ -58922,7 +58939,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="470" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>428</v>
       </c>
@@ -59044,7 +59061,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="471" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>393</v>
       </c>
@@ -59166,7 +59183,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="472" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>394</v>
       </c>
@@ -59288,7 +59305,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="473" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>395</v>
       </c>
@@ -59410,7 +59427,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="474" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>106</v>
       </c>
@@ -59532,7 +59549,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="475" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>259</v>
       </c>
@@ -59654,7 +59671,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="476" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>120</v>
       </c>
@@ -59776,7 +59793,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="477" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>429</v>
       </c>
@@ -59898,7 +59915,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="478" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>118</v>
       </c>
@@ -60020,7 +60037,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="479" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>397</v>
       </c>
@@ -60142,7 +60159,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="480" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>121</v>
       </c>
@@ -60264,7 +60281,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="481" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>122</v>
       </c>
@@ -60386,7 +60403,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="482" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>430</v>
       </c>
@@ -60508,7 +60525,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="483" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>119</v>
       </c>
@@ -60630,7 +60647,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="484" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>123</v>
       </c>
@@ -60752,7 +60769,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="485" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>361</v>
       </c>
@@ -60874,7 +60891,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="486" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>398</v>
       </c>
@@ -60996,7 +61013,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="487" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>260</v>
       </c>
@@ -61118,7 +61135,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="488" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>129</v>
       </c>
@@ -61240,7 +61257,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="489" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>128</v>
       </c>
@@ -61362,7 +61379,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="490" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>362</v>
       </c>
@@ -61484,7 +61501,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="491" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>263</v>
       </c>
@@ -61606,7 +61623,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="492" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>125</v>
       </c>
@@ -61728,7 +61745,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="493" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>127</v>
       </c>
@@ -61850,7 +61867,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="494" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>431</v>
       </c>
@@ -61972,7 +61989,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="495" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>262</v>
       </c>
@@ -62094,7 +62111,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="496" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>130</v>
       </c>
@@ -62216,7 +62233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="497" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>275</v>
       </c>
@@ -62338,7 +62355,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="498" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>261</v>
       </c>
@@ -62460,7 +62477,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="499" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>264</v>
       </c>
@@ -62582,7 +62599,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="500" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>265</v>
       </c>
@@ -62704,7 +62721,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="501" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>267</v>
       </c>
@@ -62826,7 +62843,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="502" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>126</v>
       </c>
@@ -62948,7 +62965,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="503" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>396</v>
       </c>
@@ -63070,7 +63087,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="504" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>399</v>
       </c>
@@ -63192,7 +63209,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="505" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>403</v>
       </c>
@@ -63314,7 +63331,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="506" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>400</v>
       </c>
@@ -63436,7 +63453,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="507" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>363</v>
       </c>
@@ -63558,7 +63575,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="508" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>366</v>
       </c>
@@ -63680,7 +63697,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="509" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>132</v>
       </c>
@@ -63802,7 +63819,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="510" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>274</v>
       </c>
@@ -63924,7 +63941,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="511" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>369</v>
       </c>
@@ -64046,7 +64063,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="512" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>268</v>
       </c>
@@ -64168,7 +64185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="513" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>364</v>
       </c>
@@ -64290,7 +64307,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="514" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>365</v>
       </c>
@@ -64412,7 +64429,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="515" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>266</v>
       </c>
@@ -64534,7 +64551,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="516" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>402</v>
       </c>
@@ -64656,7 +64673,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="517" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>404</v>
       </c>
@@ -64778,7 +64795,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="518" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>432</v>
       </c>
@@ -64900,7 +64917,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="519" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>133</v>
       </c>
@@ -65022,7 +65039,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="520" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>272</v>
       </c>
@@ -65144,7 +65161,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="521" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>134</v>
       </c>
@@ -65266,7 +65283,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="522" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>269</v>
       </c>
@@ -65388,7 +65405,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="523" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>271</v>
       </c>
@@ -65510,7 +65527,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="524" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>270</v>
       </c>
@@ -65632,7 +65649,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="525" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>433</v>
       </c>
@@ -65754,7 +65771,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="526" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>367</v>
       </c>
@@ -65876,7 +65893,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="527" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>276</v>
       </c>
@@ -65998,7 +66015,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="528" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>368</v>
       </c>
@@ -66120,7 +66137,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="529" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>124</v>
       </c>
@@ -66242,7 +66259,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="530" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>278</v>
       </c>
@@ -66364,7 +66381,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="531" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>135</v>
       </c>
@@ -66486,7 +66503,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="532" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>370</v>
       </c>
@@ -66608,7 +66625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="533" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>405</v>
       </c>
@@ -66730,7 +66747,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="534" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>137</v>
       </c>
@@ -66852,7 +66869,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="535" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>138</v>
       </c>
@@ -66974,7 +66991,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="536" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>279</v>
       </c>
@@ -67096,7 +67113,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="537" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>281</v>
       </c>
@@ -67218,7 +67235,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="538" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>273</v>
       </c>
@@ -67340,7 +67357,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="539" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>280</v>
       </c>
@@ -67462,7 +67479,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="540" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>140</v>
       </c>
@@ -67584,7 +67601,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="541" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>406</v>
       </c>
@@ -67706,7 +67723,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="542" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>286</v>
       </c>
@@ -67828,7 +67845,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="543" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>282</v>
       </c>
@@ -67950,7 +67967,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="544" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>143</v>
       </c>
@@ -68072,7 +68089,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="545" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>142</v>
       </c>
@@ -68194,7 +68211,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="546" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>434</v>
       </c>
@@ -68316,7 +68333,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="547" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>371</v>
       </c>
@@ -68438,7 +68455,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="548" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>141</v>
       </c>
@@ -68560,7 +68577,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="549" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>408</v>
       </c>
@@ -68682,7 +68699,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="550" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>284</v>
       </c>
@@ -68804,7 +68821,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="551" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>145</v>
       </c>
@@ -68926,7 +68943,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="552" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>293</v>
       </c>
@@ -69048,7 +69065,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="553" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>373</v>
       </c>
@@ -69170,7 +69187,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="554" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>144</v>
       </c>
@@ -69292,7 +69309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="555" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>372</v>
       </c>
@@ -69414,7 +69431,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="556" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>435</v>
       </c>
@@ -69536,7 +69553,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="557" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>285</v>
       </c>
@@ -69658,7 +69675,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="558" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>287</v>
       </c>
@@ -69780,7 +69797,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="559" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>283</v>
       </c>
@@ -69902,7 +69919,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="560" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>410</v>
       </c>
@@ -70024,7 +70041,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="561" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>409</v>
       </c>
@@ -70146,7 +70163,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="562" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>149</v>
       </c>
@@ -70268,7 +70285,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="563" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>290</v>
       </c>
@@ -70390,7 +70407,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="564" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>288</v>
       </c>
@@ -70512,7 +70529,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="565" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>147</v>
       </c>
@@ -70634,7 +70651,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="566" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>298</v>
       </c>
@@ -70756,7 +70773,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="567" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>148</v>
       </c>
@@ -70878,7 +70895,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="568" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>291</v>
       </c>
@@ -71000,7 +71017,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="569" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>294</v>
       </c>
@@ -71122,7 +71139,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="570" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>289</v>
       </c>
@@ -71244,7 +71261,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="571" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>150</v>
       </c>
@@ -71366,7 +71383,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="572" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>151</v>
       </c>
@@ -71488,7 +71505,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="573" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>153</v>
       </c>
@@ -71610,7 +71627,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="574" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>154</v>
       </c>
@@ -71732,7 +71749,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="575" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>303</v>
       </c>
@@ -71854,7 +71871,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="576" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>156</v>
       </c>
@@ -71976,7 +71993,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="577" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>155</v>
       </c>
@@ -72098,7 +72115,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="578" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>306</v>
       </c>
@@ -72220,7 +72237,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="579" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>299</v>
       </c>
@@ -72342,7 +72359,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="580" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>152</v>
       </c>
@@ -72464,7 +72481,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="581" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>297</v>
       </c>
@@ -72586,7 +72603,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="582" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>300</v>
       </c>
@@ -72708,7 +72725,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="583" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>302</v>
       </c>
@@ -72830,7 +72847,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="584" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>308</v>
       </c>
@@ -72952,7 +72969,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="585" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>310</v>
       </c>
@@ -73074,7 +73091,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="586" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>295</v>
       </c>
@@ -73196,7 +73213,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="587" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>157</v>
       </c>
@@ -73318,7 +73335,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="588" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>159</v>
       </c>
@@ -73440,7 +73457,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="589" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>307</v>
       </c>
@@ -73562,7 +73579,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="590" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>301</v>
       </c>
@@ -73684,7 +73701,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="591" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>311</v>
       </c>
@@ -73806,7 +73823,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="592" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>161</v>
       </c>
@@ -73928,7 +73945,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="593" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>162</v>
       </c>
@@ -74050,7 +74067,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="594" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>309</v>
       </c>
@@ -74172,7 +74189,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="595" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>318</v>
       </c>
@@ -74294,7 +74311,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="596" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>304</v>
       </c>
@@ -74416,7 +74433,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="597" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>375</v>
       </c>
@@ -74538,7 +74555,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="598" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>314</v>
       </c>
@@ -74660,7 +74677,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="599" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
         <v>164</v>
       </c>
@@ -74782,7 +74799,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="600" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
         <v>315</v>
       </c>
@@ -74904,7 +74921,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="601" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
         <v>167</v>
       </c>
@@ -75026,7 +75043,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="602" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
         <v>169</v>
       </c>
@@ -75148,7 +75165,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="603" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
         <v>163</v>
       </c>
@@ -75270,7 +75287,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="604" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>319</v>
       </c>
@@ -75392,7 +75409,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="605" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>170</v>
       </c>
@@ -75514,7 +75531,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="606" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>171</v>
       </c>
@@ -75636,7 +75653,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="607" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>172</v>
       </c>
@@ -75758,7 +75775,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="608" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>173</v>
       </c>
@@ -75880,7 +75897,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="609" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>316</v>
       </c>
@@ -76002,7 +76019,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="610" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>313</v>
       </c>
@@ -76124,7 +76141,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="611" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>322</v>
       </c>
@@ -76246,7 +76263,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="612" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>317</v>
       </c>
@@ -76368,7 +76385,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="613" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>377</v>
       </c>
@@ -76490,7 +76507,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="614" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>168</v>
       </c>
@@ -76612,7 +76629,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="615" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>175</v>
       </c>
@@ -76734,7 +76751,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="616" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>174</v>
       </c>
@@ -76856,7 +76873,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="617" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>323</v>
       </c>
@@ -76978,7 +76995,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="618" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>327</v>
       </c>
@@ -77100,7 +77117,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="619" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>330</v>
       </c>
@@ -77222,7 +77239,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="620" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>376</v>
       </c>
@@ -77344,7 +77361,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="621" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>415</v>
       </c>
@@ -77466,7 +77483,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="622" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>179</v>
       </c>
@@ -77588,7 +77605,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="623" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>412</v>
       </c>
@@ -77710,7 +77727,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="624" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>328</v>
       </c>
@@ -77832,7 +77849,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="625" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>413</v>
       </c>
@@ -77954,7 +77971,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="626" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>324</v>
       </c>
@@ -78076,7 +78093,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="627" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>177</v>
       </c>
@@ -78198,7 +78215,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="628" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>326</v>
       </c>
@@ -78320,7 +78337,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="629" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>334</v>
       </c>
@@ -78442,7 +78459,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="630" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>178</v>
       </c>
@@ -78564,7 +78581,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="631" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>338</v>
       </c>
@@ -78686,7 +78703,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="632" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>414</v>
       </c>
@@ -78808,7 +78825,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="633" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>331</v>
       </c>
@@ -78930,7 +78947,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="634" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>181</v>
       </c>
@@ -79052,7 +79069,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="635" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>332</v>
       </c>
@@ -79174,7 +79191,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="636" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>378</v>
       </c>
@@ -79296,7 +79313,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="637" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>180</v>
       </c>
@@ -79418,7 +79435,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="638" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>336</v>
       </c>
@@ -79540,7 +79557,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="639" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
         <v>333</v>
       </c>
@@ -79662,7 +79679,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="640" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
         <v>436</v>
       </c>
@@ -79784,8 +79801,26 @@
         <v>43</v>
       </c>
     </row>
+    <row r="641" spans="32:32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="AF641">
+        <f>((D74-AB74)/D74)/((C74-AA74)/C74)</f>
+        <v>27.701486707083262</v>
+      </c>
+    </row>
+    <row r="642" spans="32:32" x14ac:dyDescent="0.2">
+      <c r="AF642">
+        <f>((D439-AB439)/D439)/((C439-AA439)/C439)</f>
+        <v>-22.192228906573973</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN640" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AN641" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="INDR"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>